--- a/artfynd/A 16160-2026 artfynd.xlsx
+++ b/artfynd/A 16160-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131995368</v>
       </c>
       <c r="B2" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131995376</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131995344</v>
       </c>
       <c r="B4" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131995383</v>
       </c>
       <c r="B5" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131995313</v>
       </c>
       <c r="B6" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16160-2026 artfynd.xlsx
+++ b/artfynd/A 16160-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131995368</v>
       </c>
       <c r="B2" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131995376</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131995344</v>
       </c>
       <c r="B4" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131995383</v>
       </c>
       <c r="B5" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131995313</v>
       </c>
       <c r="B6" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16160-2026 artfynd.xlsx
+++ b/artfynd/A 16160-2026 artfynd.xlsx
@@ -885,7 +885,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131995344</v>
+        <v>131995383</v>
       </c>
       <c r="B4" t="n">
         <v>57953</v>
@@ -924,14 +924,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skansudden, Kallsedet, Jmt</t>
+          <t>Skansudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>399483</v>
+        <v>399633</v>
       </c>
       <c r="R4" t="n">
-        <v>7065229</v>
+        <v>7065268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131995383</v>
+        <v>131995344</v>
       </c>
       <c r="B5" t="n">
         <v>57953</v>
@@ -1029,14 +1029,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skansudden, Jmt</t>
+          <t>Skansudden, Kallsedet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>399633</v>
+        <v>399483</v>
       </c>
       <c r="R5" t="n">
-        <v>7065268</v>
+        <v>7065229</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 16160-2026 artfynd.xlsx
+++ b/artfynd/A 16160-2026 artfynd.xlsx
@@ -885,7 +885,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131995383</v>
+        <v>131995344</v>
       </c>
       <c r="B4" t="n">
         <v>57953</v>
@@ -924,14 +924,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skansudden, Jmt</t>
+          <t>Skansudden, Kallsedet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>399633</v>
+        <v>399483</v>
       </c>
       <c r="R4" t="n">
-        <v>7065268</v>
+        <v>7065229</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131995344</v>
+        <v>131995383</v>
       </c>
       <c r="B5" t="n">
         <v>57953</v>
@@ -1029,14 +1029,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skansudden, Kallsedet, Jmt</t>
+          <t>Skansudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>399483</v>
+        <v>399633</v>
       </c>
       <c r="R5" t="n">
-        <v>7065229</v>
+        <v>7065268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 16160-2026 artfynd.xlsx
+++ b/artfynd/A 16160-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131995368</v>
+        <v>132555041</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skansudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399580</v>
+        <v>399766</v>
       </c>
       <c r="R2" t="n">
-        <v>7065308</v>
+        <v>7065278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,65 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Jönsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Jönsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131995376</v>
+        <v>132555427</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>78393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399591</v>
+        <v>399766</v>
       </c>
       <c r="R3" t="n">
-        <v>7065283</v>
+        <v>7065278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tobias Jönsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Jönsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131995344</v>
+        <v>132555275</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>83363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skansudden, Kallsedet, Jmt</t>
+          <t>Skansudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>399483</v>
+        <v>399766</v>
       </c>
       <c r="R4" t="n">
-        <v>7065229</v>
+        <v>7065278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,65 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Jönsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Jönsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131995383</v>
+        <v>132555572</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>399633</v>
+        <v>399766</v>
       </c>
       <c r="R5" t="n">
-        <v>7065268</v>
+        <v>7065278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tobias Jönsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tobias Jönsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131995313</v>
+        <v>132555234</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>83358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,42 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skansudden, Kallsedet, Jmt</t>
+          <t>Skansudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>399480</v>
+        <v>399766</v>
       </c>
       <c r="R6" t="n">
-        <v>7065262</v>
+        <v>7065278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,15 +1148,540 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131995313</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skansudden, Kallsedet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>399480</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7065262</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Tobias Jönsson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Tobias Jönsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131995344</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skansudden, Kallsedet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>399483</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7065229</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Jönsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Jönsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131995368</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skansudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>399580</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7065308</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Jönsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Jönsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131995376</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skansudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>399591</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7065283</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Jönsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Jönsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131995383</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skansudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>399633</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7065268</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Jönsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Jönsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
